--- a/docs/swctx-vs-ctxe.xlsx
+++ b/docs/swctx-vs-ctxe.xlsx
@@ -8,8 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tong quan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark co cap" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verdicts model" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark do that" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ma tran tinh nang" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verdicts model" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap va Roadmap" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,20 +31,26 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="001F3864"/>
       <sz val="14"/>
     </font>
     <font>
       <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="10"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -51,17 +59,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,28 +88,31 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00B0B0B0"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00B0B0B0"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00B0B0B0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00B0B0B0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -104,6 +120,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -473,364 +492,364 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>swctx vs ctxe — Ma trận so sánh</t>
+          <t>swctx vs ctxe — So sánh hai engine retrieval</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Nguồn: bench/engine_ab_results.json + JOURNAL.md — đo trên máy thật, 2026-09-19</t>
+          <t>Nguồn: engine_ab (22 query VN) + parity_probe (18 tool) + ask_full_misses (9/9 miss) — đo trên MCP stdio thật, 2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Hạng mục</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>swctx (local)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>ctxe (server)</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Ghi chú</t>
+          <t>KẾT LUẬN NHANH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Vai trò</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>L1 — retrieval phản xạ</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>L2 — synthesis bằng LLM</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Bổ sung, không thay thế</t>
+          <t>Union coverage</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>swctx search 13/22 (59%) free ~100ms</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>ctxe ask_context cứu 9/9 miss còn lại</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Hai engine ghép đôi = 22/22 (100%) probe</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Chạy ở đâu</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Điểm quyết định</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>100% Mac local</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Engine local + server ctxe</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Chi phí</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>0 đồng</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Credits mỗi ask_context</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
+          <t>Mỗi query L1 trả lời ngay, không tốn gì</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>L2 trả credits + 12-65s nhưng cứu cả vn_to_en</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Không thay thế — bổ sung</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Riêng tư</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Dữ liệu không rời máy</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Query/chunk lên server</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Hạng mục</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>swctx</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>ctxe</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Số MCP tools</t>
+          <t>Vai trò kiến trúc</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>L1 — retrieval phản xạ (local)</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>L2 — oracle synthesis (server LLM)</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>swctx: +search,+context_pack,+prime,+put_record; ctxe: +ask_context,+compose_answer</t>
+          <t>Dual-engine by design</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Search NL toàn workspace</t>
+          <t>Chạy ở đâu</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CÓ (search)</t>
+          <t>100% on-device Mac</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>KHÔNG có</t>
+          <t>Index local + LLM server ctxe</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>ctxe chỉ có tree filter + inspect_path scoped</t>
+          <t>swctx offline hoàn toàn</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>find_definitions</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>CÓ — 3/4 @ 12ms</t>
+          <t>Chi phí / query</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>$0 — không giới hạn</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>CÓ — 3/4 @ 7ms</t>
+          <t>Credits cho ask_context/fast_understand; symbol/tree/records free</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Parity, cùng hit set</t>
+          <t>16/18 tool ctxe vẫn free local</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>find_usages</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>CÓ</t>
+          <t>Privacy</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Query + code không rời máy</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>CÓ</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
+          <t>Query + evidence gửi server khi ask</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>swctx an toàn cho code nhạy cảm</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>inspect_path</t>
+          <t>Latency retrieval</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Query scoped, delegate hybrid</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Directory-scoped, không workspace-wide</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
+          <t>p50 ~100ms, p95 ~620ms</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>find_defs p50 7ms; tree 41ms</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ctxe nhanh hơn ở surface free</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Graph (expand/neighbors/paths/impact)</t>
+          <t>Latency synthesis</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>CÓ ~10-25ms</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>CÓ + strategy arg</t>
+          <t>context_pack deterministic ~giây</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>ask_context 12-65s + record hop</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Hòa</t>
+          <t>ctxe sâu hơn nhưng chậm</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>LLM synthesis (ask/compose)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>KHÔNG (cố ý)</t>
+          <t>NL search ngữ nghĩa</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>search: FTS+vector hybrid, recall 59%</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>CÓ — 4/4 hit qua record</t>
+          <t>KHÔNG có surface NL retrieval free</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>L2 rescue được cả vn_to_en misses</t>
+          <t>Điểm khác biệt lớn nhất</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Records/memory</t>
+          <t>vn → en gap</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>put_record + global ledger, anchor stale-check</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>search_records + ask records</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
+          <t>0/5 (yếu điểm đã đo)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>ask_context cứu 2/2 vn_to_en sampled</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>P2 roadmap của swctx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Watcher freshness</t>
+          <t>Graph quality</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>6 launchd jobs, drift-exit</t>
+          <t>edges ít hơn nhưng đúng; get_impact hydrated</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>daemon watch</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
+          <t>edges nhiều hơn, get_impact thin (hop+score)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>swctx thực dụng hơn</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Cold start</t>
+          <t>Records/memory</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>0.9s (sidecar)</t>
+          <t>GlobalRecords + usage_events ledger (mới)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
+          <t>records + ask history server-side</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Parity cơ chế, khác phạm vi</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>p95 retrieval latency</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>~102-116ms</t>
+          <t>Telemetry adoption</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>usage_events + swctx stats (P1, live)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>tree proxy 424ms / ask 20-60s</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
+          <t>không có tương đương phía client</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>swctx tự đo được adoption</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Vietnamese diacritics</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>folded col + phrase leg (đo được)</t>
+          <t>Cài đặt/vận hành</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>1 binary, 6 watcher launchd, install-agent</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
+          <t>CLI + daemon + server dependency</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>swctx đơn giản hơn nhiều</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -841,319 +860,301 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Paired benchmark — 22 query VN probe, cùng workspace, cùng expected</t>
+          <t>Paired benchmark — 22 query VN, cùng workspace, file-recall@5</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Nguồn: bench/engine_ab_results.json + JOURNAL.md — đo trên máy thật, 2026-09-19</t>
+          <t>Gold path KHÔNG truyền vào retrieval call; ctxe index đã verify chứa đủ 22/22 expected path trước khi chấm</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Surface</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>n queries</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Hits@5</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Recall@5</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>p50 ms</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>p95 ms</t>
         </is>
       </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Nhận xét</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>ctxe · ask_context min, no compose</t>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>swctx · search (hybrid)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>20335.9</v>
+        <v>101.4</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>60229.3</v>
+        <v>621.4</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Surface NL retrieval duy nhất free — L1 backbone</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>swctx · search on concept_flow</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Mạnh nhất ở path-aware (82%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>swctx · find_definitions</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Parity ctxe</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
           <t>ctxe · find_definitions</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>6.7</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F8" s="4" t="n">
         <v>7.3</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>ctxe:none</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>ctxe · workspace_tree (raw NL)</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>41.2</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>208.7</v>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Parity swctx, nhanh hơn ~2x</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>ctxe · workspace_tree (token sweep)</t>
+          <t>ctxe · workspace_tree raw NL</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
         <v>11</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>0.2727</v>
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>424.2</v>
+        <v>41.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1717.1</v>
+        <v>208.7</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Substring filter — không phải semantic search</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>swctx · find_definitions</t>
+          <t>ctxe · workspace_tree token-sweep</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>0.75</v>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>12.2</v>
+        <v>424.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.8</v>
+        <v>1717.1</v>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Workaround ≤12 calls/query — vẫn yếu</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>swctx · search (hybrid NL)</t>
+          <t>ctxe · ask_context live wire</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>13</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>0.5909</v>
+        <v>2</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>101.4</v>
+        <v>20335.9</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>621.4</v>
+        <v>60229.3</v>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Live response thiếu file_path — cần record hop</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>ctxe · ask_context durable record</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>KẾT LUẬN</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>9/10 (record 9/9 miss + seo-01); L2 rescue thật</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Union swctx+ctxe coverage</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>0.773</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>swctx alone (search+defs)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>ask_context record-view (rescue swctx misses)</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>20336</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>60229</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>ctxe queries không có surface nào</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Miss-rescue: 9/9 query swctx search miss đều được ctxe ask_context record cứu (rank 1-3); crm-08 còn được find_definitions cứu free.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1164,12 +1165,661 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Toàn bộ tool surface — 20 swctx / 18 ctxe (16 shared)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>swctx</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>ctxe</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Verdict đo</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Chi tiết</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>search</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>swctx-only</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>NL hybrid retrieval — surface ctxe không có bản free</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>context_pack</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>swctx-only</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Deterministic context pack, không cần LLM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>put_record</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>swctx-only</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Ghi record vào fleet ledger local</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>prime</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>swctx-only</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Warm embedder + index check nhanh</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>ask_context</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>ctxe-only</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Server synthesis — record cứu 9/9 miss; trả credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>compose_answer</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>ctxe-only</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Verified live: record 19 → answer+confidence, 10.5s</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>find_definitions</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>parity 3/4</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Cùng hit/miss cùng query; ctxe p50 7ms vs 12ms</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>find_usages</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>swctx ≥ ctxe</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>tom_tat 3v3 · format_fragment 2v1 · ghi_quyet_dinh 0v0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>inspect_path</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>50 chunks cùng dir; ctxe thêm has_more/mode</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>fetch_chunks</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Round-trip cùng file so_tay.py cả 2 bên</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>graph_neighbors</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>parity+</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>swctx resolve dst_name+edge_kind; ctxe 9 neighbors</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>graph_expand</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>parity-empty</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Cùng rỗng trên chunk probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>graph_paths</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>chưa probe</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Mechanical parity surface</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>get_impact</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>swctx hydrated</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>swctx trả full chunk info; ctxe chỉ hop+score</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>get_workspace_tree</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>ctxe scored</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>ctxe: substring filter (0% raw NL); swctx callers dùng search</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>get_status</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Cả 2 báo indexed + counts; key layout khác</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>list_workspaces</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>khác semantics</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>swctx 23 indexed dirs; ctxe 9 accepted catalog</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>list_records</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>ctxe có ask records; swctx ledger mới (usage_events)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>search_records</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Cả 2 đáp đúng shape; nội dung theo usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>get_record</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Cả 2 fetch đúng; swctx error envelope sạch</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>fast_understand</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>khác bản chất</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>swctx: card deterministic local free; ctxe: server synthesis trả credits</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>index_workspace</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>có</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>parity ops</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Cả 2 index workspace; khác backend</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1177,48 +1827,68 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Quyết định model/reranker — đo trước quyết sau</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Nguồn: bench/engine_ab_results.json + JOURNAL.md — đo trên máy thật, 2026-09-19</t>
+          <t>Quyết định model/reranker — đo offline trước khi đổi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Ứng viên</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Loại</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Kết quả đo</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Lý do</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Ứng viên</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Loại</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Kết quả đo</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Lý do</t>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>distiluse-multi (live default)</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>embedder</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>sem leg 1/22 probe</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>GIỮ (baseline)</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Nhanh ~7ms; VN yếu nhưng hybrid FTS gánh</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>distiluse-multi (live default)</t>
+          <t>bge-m3 (568M, XLM-R)</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1228,24 +1898,24 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>sem leg 1/22 probe</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>GIỮ (baseline)</t>
+          <t>cứu 4/5 miss · ~410ms/embed</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>LOẠI (latency)</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Nhanh ~7ms; yếu VN nhưng không ai thay được cả hai</t>
+          <t>Quality GO nhưng quá gate p95 3-7×</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>bge-m3 (568M, XLM-R)</t>
+          <t>e5-large-instruct (1.1G)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1255,317 +1925,234 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>cứu 4/5 miss · ~410ms/embed</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>LOẠI (latency)</t>
+          <t>net churn 0 trên probe</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>LOẠI</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>Quality GO nhưng quá gate p95 3-7×</t>
+          <t>Không cứu thêm miss nào — d2691ed</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>multilingual-e5-base (278M)</t>
+          <t>reranker v2m3/v3 spike</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>embedder</t>
+          <t>reranker</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>1/9 cứu + 5 regression · ~50ms</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>LOẠI (quality)</t>
+          <t>đo trên worktree riêng</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>TREO</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Cosine nén 0.78-0.89, yếu vn_to_en</t>
+          <t>Chờ telemetry chỉ ra query class cần rerank</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>e5-large-instruct (560M)</t>
+          <t>translation vn→en (P2)</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>embedder</t>
+          <t>retrieval fix</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>5 cứu / 5 đuổi = net 0 · 21.6ms MPS</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>LOẠI (net churn)</t>
+          <t>ctxe ask cứu 2/2 vn_to_en</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>PROBE TIẾP</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Mạnh CRM 10/11 nhưng bleed P8</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>amberoad mBERT</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>reranker</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>neutral</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>LOẠI</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Prose-bias ≠ code</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>bge-reranker-v2-m3</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>reranker</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>7/16 · 2817ms/cặp</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>LOẠI</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Chậm 200×</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>jina-reranker-v2</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>reranker</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>13/22 neutral · 1567ms/cặp</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>LOẠI</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>3/3 reranker out — domain-bound</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>folded col + tail-fill</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>lexical</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>8→10/16</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>NHẬN</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>Cứu dấu VN, zero regression</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>folded path-phrase leg</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>lexical</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>10→11/16</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>NHẬN</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>chấm công → cham_cong.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>parallel hybrid legs</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>perf</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>150→95-125ms</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>NHẬN</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>Trong gate p95</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>vector sidecar</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>perf</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>cold 3.2→0.9s</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>NHẬN</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>vec_snapshot persistent</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>ops</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>kill-safe reindex + 5 test</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>NHẬN</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Đóng incident CRM 0-vector</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>watcher drift-exit + Store guard</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>ops</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>ledger check + abort()</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>NHẬN</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>Binary cũ tự thay</t>
+          <t>Lever duy nhất còn lại cho +5/22</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Để swctx tối ưu hơn ctxe — gap đo được + việc tiếp theo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Pri</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Việc</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Vì sao (bằng chứng)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>Trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Usage telemetry trong MCP</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Đo adoption thật: tool nào được gọi, query nào 0-hit, p95 thật — usage_events ledger + swctx stats</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>DONE 3ac98c7 · live</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>vn_to_en translation probe</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>0/5 vn_to_en — gap lớn nhất; ctxe synthesis cứu được chứng minh retrieval-side fix có giá trị</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>NEXT — chờ telemetry + probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Release packaging</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>release.sh: build→install→selftest→tag — đóng gói tái tạo được</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Corruption-injection gates</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Inject sidecar/model corrupt vào nightly — khóa class bug audit tìm ra</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>chưa làm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Synthesis cho swctx?</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>ctxe ask cứu 9/9 miss — swctx context_pack deterministic chưa đủ sâu; cân nhắc optional LLM hook local</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>quyết định sản phẩm</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>